--- a/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
+++ b/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
+++ b/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
+++ b/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -456,7 +456,7 @@
     <t>Mission Context</t>
   </si>
   <si>
-    <t>Links radiation exposure to specific space missions</t>
+    <t>Links clinical observations and events to specific space missions</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
+++ b/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
+++ b/docs/StructureDefinition-psychological-countermeasure-activity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/StructureDefinition/psychological-countermeasure-activity</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/psychological-countermeasure-activity</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -449,7 +452,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -469,7 +472,7 @@
     <t>isolationRisk</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/isolation-risk}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/isolation-risk}
 </t>
   </si>
   <si>
@@ -716,7 +719,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/ValueSet/stress-countermeasures-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/stress-countermeasures-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1114,7 +1117,7 @@
     <t>Use Procedure.reasonCode when a code sufficiently describes the reason.  Use Procedure.reasonReference when referencing a resource, which allows more information to be conveyed, such as onset date. Procedure.reasonCode and Procedure.reasonReference are not meant to be duplicative.  For a single reason, either Procedure.reasonCode or Procedure.reasonReference can be used.  Procedure.reasonCode may be a summary code, or Procedure.reasonReference may be used to reference a very precise definition of the reason using Condition | Observation | Procedure | DiagnosticReport | DocumentReference.  Both Procedure.reasonCode and Procedure.reasonReference can be used if they are describing different reasons for the procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/ValueSet/behavioral-health-metrics-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/behavioral-health-metrics-vs</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1619,54 +1622,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1704,7 +1709,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="61.22265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.4296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -1722,132 +1727,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1855,10 +1860,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1870,13 +1875,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1927,25 +1932,25 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>20</v>
@@ -1956,10 +1961,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1967,10 +1972,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1979,19 +1984,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2041,13 +2046,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2070,10 +2075,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2081,10 +2086,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2093,16 +2098,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2153,19 +2158,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2182,10 +2187,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2193,31 +2198,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2267,19 +2272,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2296,10 +2301,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2307,10 +2312,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2322,16 +2327,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2357,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2381,19 +2386,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2410,21 +2415,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2436,16 +2441,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2495,25 +2500,25 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -2524,21 +2529,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2550,16 +2555,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2609,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2627,7 +2632,7 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -2638,10 +2643,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2649,10 +2654,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2664,13 +2669,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2709,29 +2714,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2748,23 +2753,23 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2776,13 +2781,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2833,19 +2838,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2862,23 +2867,23 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2890,13 +2895,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2947,19 +2952,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2976,45 +2981,45 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3063,25 +3068,25 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>20</v>
@@ -3092,10 +3097,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3103,10 +3108,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3115,22 +3120,22 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3179,39 +3184,39 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3219,10 +3224,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3231,16 +3236,16 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3291,25 +3296,25 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>20</v>
@@ -3320,10 +3325,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3331,10 +3336,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3343,19 +3348,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3405,25 +3410,25 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
@@ -3434,21 +3439,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3457,16 +3462,16 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3517,25 +3522,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -3546,21 +3551,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3569,19 +3574,19 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3631,25 +3636,25 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -3660,10 +3665,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3671,31 +3676,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3721,11 +3726,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3743,28 +3748,28 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -3772,21 +3777,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3795,19 +3800,19 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3833,13 +3838,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3857,25 +3862,25 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -3886,10 +3891,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3897,10 +3902,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3909,16 +3914,16 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3945,13 +3950,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3969,28 +3974,28 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
@@ -3998,21 +4003,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4021,20 +4026,20 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4059,11 +4064,11 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4081,50 +4086,50 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4133,16 +4138,16 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4193,39 +4198,39 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4233,10 +4238,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4248,13 +4253,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4305,13 +4310,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4323,7 +4328,7 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4334,21 +4339,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4360,16 +4365,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4407,37 +4412,37 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -4448,10 +4453,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4459,10 +4464,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4471,19 +4476,19 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4533,25 +4538,25 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4562,10 +4567,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4573,10 +4578,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4585,19 +4590,19 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4623,13 +4628,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4647,25 +4652,25 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4676,10 +4681,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4687,10 +4692,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4699,19 +4704,19 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4761,25 +4766,25 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4790,10 +4795,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4801,10 +4806,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4813,19 +4818,19 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4875,25 +4880,25 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -4904,10 +4909,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4915,10 +4920,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4927,19 +4932,19 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4989,39 +4994,39 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5029,10 +5034,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5041,19 +5046,19 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5103,39 +5108,39 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5143,10 +5148,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5155,16 +5160,16 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5215,28 +5220,28 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5244,10 +5249,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5255,10 +5260,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5267,16 +5272,16 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5327,28 +5332,28 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5356,10 +5361,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5367,10 +5372,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5379,16 +5384,16 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5439,25 +5444,25 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5468,10 +5473,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5479,10 +5484,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5494,13 +5499,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5551,13 +5556,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5569,7 +5574,7 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5580,21 +5585,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5606,16 +5611,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5665,25 +5670,25 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -5694,45 +5699,45 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5781,25 +5786,25 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -5810,10 +5815,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5821,10 +5826,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5833,20 +5838,20 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5871,13 +5876,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5895,39 +5900,39 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5935,10 +5940,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5947,20 +5952,20 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6009,39 +6014,39 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6049,10 +6054,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6064,17 +6069,17 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6123,25 +6128,25 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6152,10 +6157,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6163,10 +6168,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6175,20 +6180,20 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6237,28 +6242,28 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6266,10 +6271,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6277,10 +6282,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6289,19 +6294,19 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6327,11 +6332,11 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6349,28 +6354,28 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6378,10 +6383,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6389,10 +6394,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6401,19 +6406,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6463,28 +6468,28 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6492,10 +6497,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6503,10 +6508,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6515,19 +6520,19 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6553,13 +6558,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6577,39 +6582,39 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6617,10 +6622,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6629,19 +6634,19 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6667,11 +6672,11 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6689,25 +6694,25 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
@@ -6718,10 +6723,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6729,10 +6734,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6744,16 +6749,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6803,25 +6808,25 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
@@ -6832,10 +6837,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6843,10 +6848,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6858,16 +6863,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6893,13 +6898,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6917,25 +6922,25 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
@@ -6946,10 +6951,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6957,10 +6962,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6972,17 +6977,17 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7031,25 +7036,25 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7060,10 +7065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7071,10 +7076,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7086,13 +7091,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7119,13 +7124,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7143,25 +7148,25 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7172,10 +7177,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7183,10 +7188,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7198,13 +7203,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7255,39 +7260,39 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7295,10 +7300,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7310,13 +7315,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7367,25 +7372,25 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7396,10 +7401,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7407,10 +7412,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7422,13 +7427,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7479,13 +7484,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -7497,7 +7502,7 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -7508,21 +7513,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7534,16 +7539,16 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7593,25 +7598,25 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7622,45 +7627,45 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7709,25 +7714,25 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -7738,10 +7743,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7749,10 +7754,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7764,13 +7769,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7797,13 +7802,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7821,25 +7826,25 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -7850,10 +7855,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7861,10 +7866,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7876,13 +7881,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7933,25 +7938,25 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -7962,10 +7967,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7973,10 +7978,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -7988,19 +7993,19 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8049,25 +8054,25 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8078,10 +8083,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8089,10 +8094,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8104,16 +8109,16 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8139,13 +8144,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8163,25 +8168,25 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
